--- a/Provider_Stress_Output/Summary_By_Scenario.xlsx
+++ b/Provider_Stress_Output/Summary_By_Scenario.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,27 +429,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>scenario</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>avg_distance_km</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>

--- a/Provider_Stress_Output/Summary_By_Scenario.xlsx
+++ b/Provider_Stress_Output/Summary_By_Scenario.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,27 +417,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>scenario</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>avg_distance_km</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>avg_travel_hours</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
@@ -470,7 +458,7 @@
         <v>0.85</v>
       </c>
       <c r="D2" t="n">
-        <v>9.460000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -491,7 +479,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>9.23</v>
+        <v>0.4</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -512,7 +500,7 @@
         <v>3.04</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>0.26</v>
       </c>
       <c r="E4" t="n">
         <v>15</v>
@@ -533,7 +521,7 @@
         <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="E5" t="n">
         <v>96</v>
@@ -554,7 +542,7 @@
         <v>3.75</v>
       </c>
       <c r="D6" t="n">
-        <v>11.77</v>
+        <v>0.51</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -575,7 +563,7 @@
         <v>3.75</v>
       </c>
       <c r="D7" t="n">
-        <v>11.77</v>
+        <v>0.51</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -596,7 +584,7 @@
         <v>13.32</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>0.26</v>
       </c>
       <c r="E8" t="n">
         <v>11</v>
@@ -617,7 +605,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="E9" t="n">
         <v>48</v>
@@ -638,7 +626,7 @@
         <v>3.75</v>
       </c>
       <c r="D10" t="n">
-        <v>10.62</v>
+        <v>0.46</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -659,7 +647,7 @@
         <v>3.75</v>
       </c>
       <c r="D11" t="n">
-        <v>10.85</v>
+        <v>0.47</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -680,7 +668,7 @@
         <v>11.78</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>0.26</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
@@ -701,7 +689,7 @@
         <v>14.14</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="E13" t="n">
         <v>48</v>
@@ -722,7 +710,7 @@
         <v>3.75</v>
       </c>
       <c r="D14" t="n">
-        <v>14.54</v>
+        <v>0.63</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -743,7 +731,7 @@
         <v>3.75</v>
       </c>
       <c r="D15" t="n">
-        <v>14.77</v>
+        <v>0.64</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -764,7 +752,7 @@
         <v>12.51</v>
       </c>
       <c r="D16" t="n">
-        <v>8.31</v>
+        <v>0.36</v>
       </c>
       <c r="E16" t="n">
         <v>51</v>
@@ -785,7 +773,7 @@
         <v>14.28</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="E17" t="n">
         <v>50</v>
@@ -806,7 +794,7 @@
         <v>0.08</v>
       </c>
       <c r="D18" t="n">
-        <v>12.23</v>
+        <v>0.53</v>
       </c>
       <c r="E18" t="n">
         <v>75</v>
@@ -827,7 +815,7 @@
         <v>0.09</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="E19" t="n">
         <v>77</v>
@@ -848,7 +836,7 @@
         <v>1.88</v>
       </c>
       <c r="D20" t="n">
-        <v>7.85</v>
+        <v>0.34</v>
       </c>
       <c r="E20" t="n">
         <v>95</v>
@@ -869,7 +857,7 @@
         <v>0.16</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="E21" t="n">
         <v>74</v>
@@ -890,7 +878,7 @@
         <v>0.08</v>
       </c>
       <c r="D22" t="n">
-        <v>12.23</v>
+        <v>0.53</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -911,7 +899,7 @@
         <v>0.09</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -932,7 +920,7 @@
         <v>10.48</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>0.26</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -953,7 +941,7 @@
         <v>0.16</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -974,7 +962,7 @@
         <v>0.05</v>
       </c>
       <c r="D26" t="n">
-        <v>12.23</v>
+        <v>0.53</v>
       </c>
       <c r="E26" t="n">
         <v>153</v>
@@ -995,7 +983,7 @@
         <v>0.12</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="E27" t="n">
         <v>153</v>
@@ -1016,7 +1004,7 @@
         <v>0.87</v>
       </c>
       <c r="D28" t="n">
-        <v>8.31</v>
+        <v>0.36</v>
       </c>
       <c r="E28" t="n">
         <v>154</v>
@@ -1037,7 +1025,7 @@
         <v>0.16</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>0.52</v>
       </c>
       <c r="E29" t="n">
         <v>153</v>

--- a/Provider_Stress_Output/Summary_By_Scenario.xlsx
+++ b/Provider_Stress_Output/Summary_By_Scenario.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,27 +429,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>scenario</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>method</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>util_std_dev</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>avg_travel_hours</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>overcap_weeks_total</t>
         </is>
